--- a/Excel+LAB+4+Dataset_Dmart_Cleaning_Structuring.xlsx
+++ b/Excel+LAB+4+Dataset_Dmart_Cleaning_Structuring.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8cfbbed923ba5ea5/Desktop/adv excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{84E5173C-E445-43B0-B4B8-93F9F631873B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E60DB2C7-6445-4EAD-B7B7-D624A6F56DE2}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{84E5173C-E445-43B0-B4B8-93F9F631873B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E323197C-1E3D-4E0A-9BCC-E7551A744791}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DMart Data Sale" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,7 @@
   <definedNames>
     <definedName name="category">'DMart Data Sale'!$D:$D</definedName>
     <definedName name="discount">'DMart Data Sale'!$G:$G</definedName>
+    <definedName name="orderId">'DMart Data Sale'!$A:$A</definedName>
     <definedName name="region">'DMart Data Sale'!$B:$B</definedName>
     <definedName name="sales">'DMart Data Sale'!$E:$E</definedName>
   </definedNames>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4591" uniqueCount="661">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4603" uniqueCount="671">
   <si>
     <t>Region</t>
   </si>
@@ -2024,6 +2025,36 @@
   </si>
   <si>
     <t>Total sales by Category:Electronics and region:North and discount is &gt;40%</t>
+  </si>
+  <si>
+    <t>Total orders</t>
+  </si>
+  <si>
+    <t>Count transactions made by UPI</t>
+  </si>
+  <si>
+    <t>Count transactions made by Cash</t>
+  </si>
+  <si>
+    <t>Count transactions made by Card</t>
+  </si>
+  <si>
+    <t>Find the numbers of transaction having sales value more than 4000</t>
+  </si>
+  <si>
+    <t>Find the numbers of transaction having sales value more than 4000 in north region</t>
+  </si>
+  <si>
+    <t>Find the numbers of transaction having sales value more than 4000 in south region</t>
+  </si>
+  <si>
+    <t>Find the numbers of transaction having sales value more than 4000 in east region</t>
+  </si>
+  <si>
+    <t>Find the numbers of transaction having sales value more than 4000 in west region</t>
+  </si>
+  <si>
+    <t>Total sales for customer type MEMBER and payment mode is UPI OR CARD</t>
   </si>
 </sst>
 </file>
@@ -2033,7 +2064,7 @@
   <numFmts count="3">
     <numFmt numFmtId="44" formatCode="_ &quot;₹&quot;\ * #,##0.00_ ;_ &quot;₹&quot;\ * \-#,##0.00_ ;_ &quot;₹&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="170" formatCode="&quot;₹&quot;\ #,##0.00"/>
+    <numFmt numFmtId="165" formatCode="&quot;₹&quot;\ #,##0.00"/>
   </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
@@ -2183,7 +2214,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -2288,12 +2319,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2314,9 +2358,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -2351,20 +2392,20 @@
     <xf numFmtId="0" fontId="16" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="16" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -3221,61 +3262,61 @@
     <col min="15" max="16" width="11.36328125" customWidth="1"/>
     <col min="17" max="17" width="15" customWidth="1"/>
     <col min="18" max="18" width="8.6328125" customWidth="1"/>
-    <col min="19" max="19" width="38.90625" customWidth="1"/>
-    <col min="20" max="20" width="15.08984375" customWidth="1"/>
+    <col min="19" max="19" width="67.36328125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="20.90625" customWidth="1"/>
     <col min="21" max="25" width="8.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="19" t="s">
         <v>542</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="20" t="s">
         <v>599</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="E1" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="21" t="s">
+      <c r="F1" s="20" t="s">
         <v>643</v>
       </c>
-      <c r="G1" s="22" t="s">
+      <c r="G1" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="22" t="s">
+      <c r="H1" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="22" t="s">
+      <c r="I1" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="22" t="s">
+      <c r="J1" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="22" t="s">
+      <c r="K1" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="22" t="s">
+      <c r="L1" s="21" t="s">
         <v>541</v>
       </c>
-      <c r="M1" s="22" t="s">
+      <c r="M1" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="N1" s="22" t="s">
+      <c r="N1" s="21" t="s">
         <v>644</v>
       </c>
-      <c r="O1" s="22" t="s">
+      <c r="O1" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="22" t="s">
+      <c r="P1" s="21" t="s">
         <v>543</v>
       </c>
-      <c r="Q1" s="23" t="s">
+      <c r="Q1" s="22" t="s">
         <v>10</v>
       </c>
       <c r="R1" s="1"/>
@@ -3344,10 +3385,10 @@
         <v>16</v>
       </c>
       <c r="R2" s="1"/>
-      <c r="S2" s="44" t="s">
+      <c r="S2" s="42" t="s">
         <v>645</v>
       </c>
-      <c r="T2" s="45">
+      <c r="T2" s="43">
         <f>SUMIF(Table1[payment_mode],"UPI",Table1[sales])</f>
         <v>386412.25</v>
       </c>
@@ -3414,10 +3455,10 @@
         <v>21</v>
       </c>
       <c r="R3" s="1"/>
-      <c r="S3" s="46" t="s">
+      <c r="S3" s="44" t="s">
         <v>646</v>
       </c>
-      <c r="T3" s="45">
+      <c r="T3" s="43">
         <f>SUMIF(Table1[payment_mode],"Cash",Table1[sales])</f>
         <v>522964.3</v>
       </c>
@@ -3484,10 +3525,10 @@
         <v>26</v>
       </c>
       <c r="R4" s="1"/>
-      <c r="S4" s="44" t="s">
+      <c r="S4" s="42" t="s">
         <v>656</v>
       </c>
-      <c r="T4" s="45">
+      <c r="T4" s="43">
         <f>SUMIF(Table1[payment_mode],"Card",Table1[sales])</f>
         <v>413292.63999999996</v>
       </c>
@@ -3555,7 +3596,7 @@
       </c>
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
-      <c r="T5" s="43"/>
+      <c r="T5" s="41"/>
       <c r="U5" s="1"/>
       <c r="V5" s="1"/>
       <c r="W5" s="1"/>
@@ -3619,10 +3660,10 @@
         <v>16</v>
       </c>
       <c r="R6" s="1"/>
-      <c r="S6" s="44" t="s">
+      <c r="S6" s="47" t="s">
         <v>659</v>
       </c>
-      <c r="T6" s="46">
+      <c r="T6" s="44">
         <f>SUMIFS(sales,category,"Clothing",region,"East")</f>
         <v>60655.859999999993</v>
       </c>
@@ -3689,15 +3730,14 @@
         <v>34</v>
       </c>
       <c r="R7" s="1"/>
-      <c r="S7" s="44" t="s">
+      <c r="S7" s="47" t="s">
         <v>660</v>
       </c>
-      <c r="T7" s="46"/>
-      <c r="U7" s="46"/>
-      <c r="V7" s="46">
+      <c r="T7" s="44">
         <f>SUMIFS(sales,category,"Electronics",region,"North",discount,"&gt;0.40")</f>
         <v>36091.269999999997</v>
       </c>
+      <c r="U7" s="46"/>
       <c r="W7" s="1"/>
       <c r="X7" s="1"/>
       <c r="Y7" s="1"/>
@@ -3824,8 +3864,13 @@
         <v>38</v>
       </c>
       <c r="R9" s="1"/>
-      <c r="S9" s="1"/>
-      <c r="T9" s="1"/>
+      <c r="S9" s="45" t="s">
+        <v>661</v>
+      </c>
+      <c r="T9" s="44">
+        <f>COUNT(sales)</f>
+        <v>498</v>
+      </c>
       <c r="U9" s="1"/>
       <c r="V9" s="1"/>
       <c r="W9" s="1"/>
@@ -3889,8 +3934,13 @@
         <v>40</v>
       </c>
       <c r="R10" s="1"/>
-      <c r="S10" s="1"/>
-      <c r="T10" s="1"/>
+      <c r="S10" s="45" t="s">
+        <v>662</v>
+      </c>
+      <c r="T10" s="44">
+        <f>COUNTIF(M:M,"UPI")</f>
+        <v>149</v>
+      </c>
       <c r="U10" s="1"/>
       <c r="V10" s="1"/>
       <c r="W10" s="1"/>
@@ -3954,8 +4004,13 @@
         <v>21</v>
       </c>
       <c r="R11" s="1"/>
-      <c r="S11" s="1"/>
-      <c r="T11" s="1"/>
+      <c r="S11" s="45" t="s">
+        <v>663</v>
+      </c>
+      <c r="T11" s="44">
+        <f>COUNTIF(M:M,"Cash")</f>
+        <v>185</v>
+      </c>
       <c r="U11" s="1"/>
       <c r="V11" s="1"/>
       <c r="W11" s="1"/>
@@ -4019,8 +4074,13 @@
         <v>43</v>
       </c>
       <c r="R12" s="1"/>
-      <c r="S12" s="1"/>
-      <c r="T12" s="1"/>
+      <c r="S12" s="45" t="s">
+        <v>664</v>
+      </c>
+      <c r="T12" s="44">
+        <f>COUNTIF(M:M,"Card")</f>
+        <v>164</v>
+      </c>
       <c r="U12" s="1"/>
       <c r="V12" s="1"/>
       <c r="W12" s="1"/>
@@ -4149,9 +4209,13 @@
         <v>29</v>
       </c>
       <c r="R14" s="1"/>
-      <c r="S14" s="1"/>
-      <c r="T14" s="1"/>
-      <c r="U14" s="1"/>
+      <c r="S14" s="45" t="s">
+        <v>665</v>
+      </c>
+      <c r="T14" s="44">
+        <f>COUNTIF(sales,"&gt;4000")</f>
+        <v>115</v>
+      </c>
       <c r="V14" s="1"/>
       <c r="W14" s="1"/>
       <c r="X14" s="1"/>
@@ -4214,9 +4278,13 @@
         <v>47</v>
       </c>
       <c r="R15" s="1"/>
-      <c r="S15" s="19"/>
-      <c r="T15" s="19"/>
-      <c r="U15" s="1"/>
+      <c r="S15" s="45" t="s">
+        <v>666</v>
+      </c>
+      <c r="T15" s="44">
+        <f>COUNTIFS(region,"North",sales,"&gt;4000")</f>
+        <v>32</v>
+      </c>
       <c r="V15" s="1"/>
       <c r="W15" s="1"/>
       <c r="X15" s="1"/>
@@ -4279,9 +4347,13 @@
         <v>38</v>
       </c>
       <c r="R16" s="1"/>
-      <c r="S16" s="19"/>
-      <c r="T16" s="19"/>
-      <c r="U16" s="1"/>
+      <c r="S16" s="45" t="s">
+        <v>667</v>
+      </c>
+      <c r="T16" s="44">
+        <f>COUNTIFS(region,"South",sales,"&gt;4000")</f>
+        <v>27</v>
+      </c>
       <c r="V16" s="1"/>
       <c r="W16" s="1"/>
       <c r="X16" s="1"/>
@@ -4344,9 +4416,13 @@
         <v>40</v>
       </c>
       <c r="R17" s="1"/>
-      <c r="S17" s="19"/>
-      <c r="T17" s="19"/>
-      <c r="U17" s="1"/>
+      <c r="S17" s="45" t="s">
+        <v>668</v>
+      </c>
+      <c r="T17" s="44">
+        <f>COUNTIFS(region,"East",sales,"&gt;4000")</f>
+        <v>29</v>
+      </c>
       <c r="V17" s="1"/>
       <c r="W17" s="1"/>
       <c r="X17" s="1"/>
@@ -4409,9 +4485,13 @@
         <v>51</v>
       </c>
       <c r="R18" s="1"/>
-      <c r="S18" s="19"/>
-      <c r="T18" s="19"/>
-      <c r="U18" s="1"/>
+      <c r="S18" s="45" t="s">
+        <v>669</v>
+      </c>
+      <c r="T18" s="44">
+        <f>COUNTIFS(region,"West",sales,"&gt;4000")</f>
+        <v>27</v>
+      </c>
       <c r="V18" s="1"/>
       <c r="W18" s="1"/>
       <c r="X18" s="1"/>
@@ -4539,9 +4619,15 @@
         <v>54</v>
       </c>
       <c r="R20" s="1"/>
-      <c r="S20" s="1"/>
-      <c r="T20" s="1"/>
-      <c r="U20" s="1"/>
+      <c r="S20" s="45" t="s">
+        <v>670</v>
+      </c>
+      <c r="T20" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="U20" s="26" t="s">
+        <v>20</v>
+      </c>
       <c r="V20" s="1"/>
       <c r="W20" s="1"/>
       <c r="X20" s="1"/>
@@ -4604,9 +4690,18 @@
         <v>38</v>
       </c>
       <c r="R21" s="1"/>
-      <c r="S21" s="1"/>
-      <c r="T21" s="1"/>
-      <c r="U21" s="1"/>
+      <c r="S21" s="44">
+        <f>COUNTIFS(L:L,"Member",M:M,"UPI")+COUNTIFS(L:L,"Member",M:M,"Card")</f>
+        <v>97</v>
+      </c>
+      <c r="T21" s="44">
+        <f>COUNTIFS(L:L,"Member",M:M,"UPI")</f>
+        <v>50</v>
+      </c>
+      <c r="U21" s="44">
+        <f>COUNTIFS(L:L,"Member",M:M,"Card")</f>
+        <v>47</v>
+      </c>
       <c r="V21" s="1"/>
       <c r="W21" s="1"/>
       <c r="X21" s="1"/>
@@ -4669,7 +4764,6 @@
         <v>57</v>
       </c>
       <c r="R22" s="1"/>
-      <c r="S22" s="1"/>
       <c r="T22" s="1"/>
       <c r="U22" s="1"/>
       <c r="V22" s="1"/>
@@ -49176,7 +49270,7 @@
       <c r="C2" t="s">
         <v>555</v>
       </c>
-      <c r="D2" s="24" t="s">
+      <c r="D2" s="23" t="s">
         <v>572</v>
       </c>
       <c r="E2" t="s">
@@ -49199,7 +49293,7 @@
       <c r="C3" t="s">
         <v>556</v>
       </c>
-      <c r="D3" s="24" t="s">
+      <c r="D3" s="23" t="s">
         <v>573</v>
       </c>
       <c r="E3" t="s">
@@ -49222,7 +49316,7 @@
       <c r="C4" t="s">
         <v>569</v>
       </c>
-      <c r="D4" s="24" t="s">
+      <c r="D4" s="23" t="s">
         <v>574</v>
       </c>
       <c r="E4" t="s">
@@ -49245,7 +49339,7 @@
       <c r="C5" t="s">
         <v>570</v>
       </c>
-      <c r="D5" s="24" t="s">
+      <c r="D5" s="23" t="s">
         <v>575</v>
       </c>
       <c r="E5" t="s">
@@ -49453,407 +49547,407 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>587</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="24" t="s">
         <v>592</v>
       </c>
-      <c r="D1" s="28"/>
+      <c r="D1" s="27"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="24" t="s">
         <v>588</v>
       </c>
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="25" t="s">
         <v>593</v>
       </c>
-      <c r="E2" s="28"/>
+      <c r="E2" s="27"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="24" t="s">
         <v>589</v>
       </c>
-      <c r="B3" s="25" t="s">
+      <c r="B3" s="24" t="s">
         <v>595</v>
       </c>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="24" t="s">
         <v>590</v>
       </c>
-      <c r="B4" s="25" t="s">
+      <c r="B4" s="24" t="s">
         <v>594</v>
       </c>
-      <c r="E4" s="29"/>
+      <c r="E4" s="28"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A5" s="25" t="s">
+      <c r="A5" s="24" t="s">
         <v>591</v>
       </c>
-      <c r="B5" s="25" t="s">
+      <c r="B5" s="24" t="s">
         <v>596</v>
       </c>
-      <c r="E5" s="29"/>
+      <c r="E5" s="28"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="24" t="s">
         <v>588</v>
       </c>
-      <c r="B6" s="25" t="s">
+      <c r="B6" s="24" t="s">
         <v>597</v>
       </c>
-      <c r="E6" s="29"/>
+      <c r="E6" s="28"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A7" s="25" t="s">
+      <c r="A7" s="24" t="s">
         <v>589</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="24" t="s">
         <v>598</v>
       </c>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="24" t="s">
         <v>590</v>
       </c>
-      <c r="B8" s="26" t="s">
+      <c r="B8" s="25" t="s">
         <v>593</v>
       </c>
-      <c r="E8" s="29"/>
+      <c r="E8" s="28"/>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A9" s="25" t="s">
+      <c r="A9" s="24" t="s">
         <v>591</v>
       </c>
-      <c r="B9" s="25" t="s">
+      <c r="B9" s="24" t="s">
         <v>595</v>
       </c>
-      <c r="E9" s="29"/>
+      <c r="E9" s="28"/>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A10" s="25" t="s">
+      <c r="A10" s="24" t="s">
         <v>588</v>
       </c>
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="24" t="s">
         <v>594</v>
       </c>
-      <c r="E10" s="29"/>
+      <c r="E10" s="28"/>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A11" s="25" t="s">
+      <c r="A11" s="24" t="s">
         <v>589</v>
       </c>
-      <c r="B11" s="25" t="s">
+      <c r="B11" s="24" t="s">
         <v>596</v>
       </c>
-      <c r="D11" s="29"/>
-      <c r="E11" s="29"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="28"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A12" s="25" t="s">
+      <c r="A12" s="24" t="s">
         <v>590</v>
       </c>
-      <c r="B12" s="25" t="s">
+      <c r="B12" s="24" t="s">
         <v>597</v>
       </c>
-      <c r="E12" s="29"/>
+      <c r="E12" s="28"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A13" s="25" t="s">
+      <c r="A13" s="24" t="s">
         <v>591</v>
       </c>
-      <c r="B13" s="25" t="s">
+      <c r="B13" s="24" t="s">
         <v>598</v>
       </c>
-      <c r="E13" s="29"/>
-      <c r="O13" s="32"/>
-      <c r="P13" s="32"/>
+      <c r="E13" s="28"/>
+      <c r="O13" s="31"/>
+      <c r="P13" s="31"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A14" s="25" t="s">
+      <c r="A14" s="24" t="s">
         <v>588</v>
       </c>
-      <c r="B14" s="26" t="s">
+      <c r="B14" s="25" t="s">
         <v>593</v>
       </c>
-      <c r="D14" s="33" t="s">
+      <c r="D14" s="32" t="s">
         <v>619</v>
       </c>
-      <c r="E14" s="33" t="s">
+      <c r="E14" s="32" t="s">
         <v>620</v>
       </c>
-      <c r="F14" s="33" t="s">
+      <c r="F14" s="32" t="s">
         <v>621</v>
       </c>
-      <c r="H14" s="32" t="s">
+      <c r="H14" s="31" t="s">
         <v>627</v>
       </c>
-      <c r="I14" s="32" t="s">
+      <c r="I14" s="31" t="s">
         <v>628</v>
       </c>
-      <c r="K14" s="33" t="s">
+      <c r="K14" s="32" t="s">
         <v>619</v>
       </c>
-      <c r="L14" s="33" t="s">
+      <c r="L14" s="32" t="s">
         <v>637</v>
       </c>
-      <c r="M14" s="33" t="s">
+      <c r="M14" s="32" t="s">
         <v>638</v>
       </c>
-      <c r="N14" s="33" t="s">
+      <c r="N14" s="32" t="s">
         <v>640</v>
       </c>
-      <c r="P14" s="35"/>
-      <c r="Q14" s="32" t="s">
+      <c r="P14" s="34"/>
+      <c r="Q14" s="31" t="s">
         <v>641</v>
       </c>
-      <c r="R14" s="32" t="s">
+      <c r="R14" s="31" t="s">
         <v>642</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A15" s="25" t="s">
+      <c r="A15" s="24" t="s">
         <v>589</v>
       </c>
-      <c r="B15" s="25" t="s">
+      <c r="B15" s="24" t="s">
         <v>595</v>
       </c>
-      <c r="D15" s="33" t="s">
+      <c r="D15" s="32" t="s">
         <v>622</v>
       </c>
-      <c r="E15" s="27">
+      <c r="E15" s="26">
         <v>98</v>
       </c>
-      <c r="F15" s="27" t="str">
+      <c r="F15" s="26" t="str">
         <f>IF(E15&gt;90,"A++",IF(E15&gt;75,"A+",IF(E15&gt;60,"A",IF(E15&gt;40,"B","Fail"))))</f>
         <v>A++</v>
       </c>
-      <c r="H15" s="32" t="s">
+      <c r="H15" s="31" t="s">
         <v>629</v>
       </c>
-      <c r="I15" s="32" t="s">
+      <c r="I15" s="31" t="s">
         <v>630</v>
       </c>
-      <c r="K15" s="33" t="s">
+      <c r="K15" s="32" t="s">
         <v>622</v>
       </c>
-      <c r="L15" s="27">
+      <c r="L15" s="26">
         <v>70000</v>
       </c>
-      <c r="M15" s="27" t="str">
+      <c r="M15" s="26" t="str">
         <f>IF(L15&gt;=75000,"15%",IF(L15&gt;=70000,"10%",IF(L15&gt;=50000,"5%",IF(L15&lt;50000,"no bonus"))))</f>
         <v>10%</v>
       </c>
-      <c r="N15" s="27"/>
-      <c r="P15" s="34"/>
+      <c r="N15" s="26"/>
+      <c r="P15" s="33"/>
       <c r="Q15">
         <v>75000</v>
       </c>
-      <c r="R15" s="34">
+      <c r="R15" s="33">
         <v>0.15</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="D16" s="33" t="s">
+      <c r="D16" s="32" t="s">
         <v>623</v>
       </c>
-      <c r="E16" s="27">
+      <c r="E16" s="26">
         <v>32</v>
       </c>
-      <c r="F16" s="27" t="str">
+      <c r="F16" s="26" t="str">
         <f>IF(E16&gt;90,"A++",IF(E16&gt;75,"A+",IF(E16&gt;60,"A",IF(E16&gt;40,"B","Fail"))))</f>
         <v>Fail</v>
       </c>
-      <c r="H16" s="32" t="s">
+      <c r="H16" s="31" t="s">
         <v>631</v>
       </c>
-      <c r="I16" s="32" t="s">
+      <c r="I16" s="31" t="s">
         <v>633</v>
       </c>
-      <c r="K16" s="33" t="s">
+      <c r="K16" s="32" t="s">
         <v>623</v>
       </c>
-      <c r="L16" s="27">
+      <c r="L16" s="26">
         <v>50000</v>
       </c>
-      <c r="M16" s="27" t="str">
+      <c r="M16" s="26" t="str">
         <f>IF(L16&gt;=75000,"15%",IF(L16&gt;=70000,"10%",IF(L16&gt;=50000,"5%",IF(L16&lt;50000,"no bonus"))))</f>
         <v>5%</v>
       </c>
-      <c r="N16" s="27"/>
-      <c r="P16" s="34"/>
+      <c r="N16" s="26"/>
+      <c r="P16" s="33"/>
       <c r="Q16">
         <v>70000</v>
       </c>
-      <c r="R16" s="34">
+      <c r="R16" s="33">
         <v>0.1</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="D17" s="33" t="s">
+      <c r="D17" s="32" t="s">
         <v>624</v>
       </c>
-      <c r="E17" s="27">
+      <c r="E17" s="26">
         <v>79</v>
       </c>
-      <c r="F17" s="27" t="str">
+      <c r="F17" s="26" t="str">
         <f>IF(E17&gt;90,"A++",IF(E17&gt;75,"A+",IF(E17&gt;60,"A",IF(E17&gt;40,"B","Fail"))))</f>
         <v>A+</v>
       </c>
-      <c r="H17" s="32" t="s">
+      <c r="H17" s="31" t="s">
         <v>632</v>
       </c>
-      <c r="I17" s="32" t="s">
+      <c r="I17" s="31" t="s">
         <v>634</v>
       </c>
-      <c r="K17" s="33" t="s">
+      <c r="K17" s="32" t="s">
         <v>624</v>
       </c>
-      <c r="L17" s="27">
+      <c r="L17" s="26">
         <v>45000</v>
       </c>
-      <c r="M17" s="27" t="str">
+      <c r="M17" s="26" t="str">
         <f>IF(L17&gt;=75000,"15%",IF(L17&gt;=70000,"10%",IF(L17&gt;=50000,"5%",IF(L17&lt;50000,"no bonus"))))</f>
         <v>no bonus</v>
       </c>
-      <c r="N17" s="27"/>
-      <c r="O17" s="32"/>
-      <c r="P17" s="34"/>
+      <c r="N17" s="26"/>
+      <c r="O17" s="31"/>
+      <c r="P17" s="33"/>
       <c r="Q17">
         <v>50000</v>
       </c>
-      <c r="R17" s="34">
+      <c r="R17" s="33">
         <v>0.05</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A18" s="27" t="s">
+      <c r="A18" s="26" t="s">
         <v>606</v>
       </c>
-      <c r="B18" s="27" t="s">
+      <c r="B18" s="26" t="s">
         <v>588</v>
       </c>
-      <c r="D18" s="33" t="s">
+      <c r="D18" s="32" t="s">
         <v>625</v>
       </c>
-      <c r="E18" s="27">
+      <c r="E18" s="26">
         <v>55</v>
       </c>
-      <c r="F18" s="27" t="str">
+      <c r="F18" s="26" t="str">
         <f>IF(E18&gt;90,"A++",IF(E18&gt;75,"A+",IF(E18&gt;60,"A",IF(E18&gt;40,"B","Fail"))))</f>
         <v>B</v>
       </c>
-      <c r="H18" s="32" t="s">
+      <c r="H18" s="31" t="s">
         <v>635</v>
       </c>
-      <c r="I18" s="32" t="s">
+      <c r="I18" s="31" t="s">
         <v>636</v>
       </c>
-      <c r="K18" s="33" t="s">
+      <c r="K18" s="32" t="s">
         <v>625</v>
       </c>
-      <c r="L18" s="27">
+      <c r="L18" s="26">
         <v>75000</v>
       </c>
-      <c r="M18" s="27" t="str">
+      <c r="M18" s="26" t="str">
         <f>IF(L18&gt;=75000,"15%",IF(L18&gt;=70000,"10%",IF(L18&gt;=50000,"5%",IF(L18&lt;50000,"no bonus"))))</f>
         <v>15%</v>
       </c>
-      <c r="N18" s="27"/>
-      <c r="Q18" s="32" t="s">
+      <c r="N18" s="26"/>
+      <c r="Q18" s="31" t="s">
         <v>639</v>
       </c>
-      <c r="R18" s="34">
+      <c r="R18" s="33">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A19" s="27" t="s">
+      <c r="A19" s="26" t="s">
         <v>609</v>
       </c>
-      <c r="B19" s="27">
+      <c r="B19" s="26">
         <v>93489</v>
       </c>
-      <c r="D19" s="33" t="s">
+      <c r="D19" s="32" t="s">
         <v>626</v>
       </c>
-      <c r="E19" s="27">
+      <c r="E19" s="26">
         <v>87</v>
       </c>
-      <c r="F19" s="27" t="str">
+      <c r="F19" s="26" t="str">
         <f>IF(E19&gt;90,"A++",IF(E19&gt;75,"A+",IF(E19&gt;60,"A",IF(E19&gt;40,"B","Fail"))))</f>
         <v>A+</v>
       </c>
-      <c r="K19" s="33" t="s">
+      <c r="K19" s="32" t="s">
         <v>626</v>
       </c>
-      <c r="L19" s="27">
+      <c r="L19" s="26">
         <v>55000</v>
       </c>
-      <c r="M19" s="27" t="str">
+      <c r="M19" s="26" t="str">
         <f>IF(L19&gt;=75000,"15%",IF(L19&gt;=70000,"10%",IF(L19&gt;=50000,"5%",IF(L19&lt;50000,"no bonus"))))</f>
         <v>5%</v>
       </c>
-      <c r="N19" s="27"/>
+      <c r="N19" s="26"/>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A20" s="27" t="s">
+      <c r="A20" s="26" t="s">
         <v>607</v>
       </c>
-      <c r="B20" s="27">
+      <c r="B20" s="26">
         <v>84798</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A21" s="27" t="s">
+      <c r="A21" s="26" t="s">
         <v>608</v>
       </c>
-      <c r="B21" s="27">
+      <c r="B21" s="26">
         <v>44890</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A22" s="27" t="s">
+      <c r="A22" s="26" t="s">
         <v>613</v>
       </c>
-      <c r="B22" s="27">
+      <c r="B22" s="26">
         <v>47927</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A23" s="27" t="s">
+      <c r="A23" s="26" t="s">
         <v>610</v>
       </c>
-      <c r="B23" s="27">
+      <c r="B23" s="26">
         <v>94899</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A24" s="27" t="s">
+      <c r="A24" s="26" t="s">
         <v>614</v>
       </c>
-      <c r="B24" s="27">
+      <c r="B24" s="26">
         <v>84290</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A25" s="27" t="s">
+      <c r="A25" s="26" t="s">
         <v>611</v>
       </c>
-      <c r="B25" s="27">
+      <c r="B25" s="26">
         <v>80950</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A26" s="27" t="s">
+      <c r="A26" s="26" t="s">
         <v>612</v>
       </c>
-      <c r="B26" s="27">
+      <c r="B26" s="26">
         <v>59860</v>
       </c>
     </row>
@@ -49879,182 +49973,182 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="29" t="s">
         <v>615</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="29" t="s">
         <v>592</v>
       </c>
-      <c r="D2" s="36" t="s">
+      <c r="D2" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="36" t="s">
+      <c r="E2" s="35" t="s">
         <v>647</v>
       </c>
-      <c r="F2" s="37" t="s">
+      <c r="F2" s="36" t="s">
         <v>588</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A3" s="31" t="s">
+      <c r="A3" s="30" t="s">
         <v>588</v>
       </c>
-      <c r="B3" s="31" t="s">
+      <c r="B3" s="30" t="s">
         <v>616</v>
       </c>
-      <c r="C3" s="25"/>
-      <c r="D3" s="38" t="s">
+      <c r="C3" s="24"/>
+      <c r="D3" s="37" t="s">
         <v>648</v>
       </c>
-      <c r="E3" s="38" t="s">
+      <c r="E3" s="37" t="s">
         <v>649</v>
       </c>
-      <c r="F3" s="40">
+      <c r="F3" s="38">
         <v>2300</v>
       </c>
-      <c r="H3" s="41" t="s">
+      <c r="H3" s="39" t="s">
         <v>658</v>
       </c>
-      <c r="I3" s="27">
+      <c r="I3" s="26">
         <f>SUMIF(D3:D8,"Fruits",F3:F8)</f>
         <v>2000</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="26" t="s">
         <v>589</v>
       </c>
-      <c r="B4" s="31" t="s">
+      <c r="B4" s="30" t="s">
         <v>617</v>
       </c>
-      <c r="D4" s="38" t="s">
+      <c r="D4" s="37" t="s">
         <v>648</v>
       </c>
-      <c r="E4" s="38" t="s">
+      <c r="E4" s="37" t="s">
         <v>650</v>
       </c>
-      <c r="F4" s="40">
+      <c r="F4" s="38">
         <v>5500</v>
       </c>
-      <c r="H4" s="42" t="s">
+      <c r="H4" s="40" t="s">
         <v>657</v>
       </c>
-      <c r="I4" s="27">
+      <c r="I4" s="26">
         <f ca="1">SUMIF(D3:D8,"",F3:F7)</f>
         <v>400</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="26" t="s">
         <v>590</v>
       </c>
-      <c r="B5" s="31" t="s">
+      <c r="B5" s="30" t="s">
         <v>594</v>
       </c>
-      <c r="D5" s="38" t="s">
+      <c r="D5" s="37" t="s">
         <v>651</v>
       </c>
-      <c r="E5" s="38" t="s">
+      <c r="E5" s="37" t="s">
         <v>652</v>
       </c>
-      <c r="F5" s="39">
+      <c r="F5" s="37">
         <v>800</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A6" s="27" t="s">
+      <c r="A6" s="26" t="s">
         <v>591</v>
       </c>
-      <c r="B6" s="31" t="s">
+      <c r="B6" s="30" t="s">
         <v>618</v>
       </c>
-      <c r="D6" s="38"/>
-      <c r="E6" s="38" t="s">
+      <c r="D6" s="37"/>
+      <c r="E6" s="37" t="s">
         <v>653</v>
       </c>
-      <c r="F6" s="39">
+      <c r="F6" s="37">
         <v>400</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A7" s="31" t="s">
+      <c r="A7" s="30" t="s">
         <v>588</v>
       </c>
-      <c r="B7" s="31" t="s">
+      <c r="B7" s="30" t="s">
         <v>598</v>
       </c>
-      <c r="D7" s="38" t="s">
+      <c r="D7" s="37" t="s">
         <v>648</v>
       </c>
-      <c r="E7" s="38" t="s">
+      <c r="E7" s="37" t="s">
         <v>654</v>
       </c>
-      <c r="F7" s="40">
+      <c r="F7" s="38">
         <v>4200</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="26" t="s">
         <v>589</v>
       </c>
-      <c r="B8" s="31" t="s">
+      <c r="B8" s="30" t="s">
         <v>616</v>
       </c>
-      <c r="D8" s="38" t="s">
+      <c r="D8" s="37" t="s">
         <v>651</v>
       </c>
-      <c r="E8" s="38" t="s">
+      <c r="E8" s="37" t="s">
         <v>655</v>
       </c>
-      <c r="F8" s="40">
+      <c r="F8" s="38">
         <v>1200</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="26" t="s">
         <v>590</v>
       </c>
-      <c r="B9" s="31" t="s">
+      <c r="B9" s="30" t="s">
         <v>617</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A10" s="27" t="s">
+      <c r="A10" s="26" t="s">
         <v>591</v>
       </c>
-      <c r="B10" s="31" t="s">
+      <c r="B10" s="30" t="s">
         <v>594</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A11" s="31" t="s">
+      <c r="A11" s="30" t="s">
         <v>588</v>
       </c>
-      <c r="B11" s="31" t="s">
+      <c r="B11" s="30" t="s">
         <v>618</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A12" s="27" t="s">
+      <c r="A12" s="26" t="s">
         <v>589</v>
       </c>
-      <c r="B12" s="31" t="s">
+      <c r="B12" s="30" t="s">
         <v>598</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A13" s="27" t="s">
+      <c r="A13" s="26" t="s">
         <v>590</v>
       </c>
-      <c r="B13" s="31" t="s">
+      <c r="B13" s="30" t="s">
         <v>616</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A14" s="27" t="s">
+      <c r="A14" s="26" t="s">
         <v>591</v>
       </c>
-      <c r="B14" s="31" t="s">
+      <c r="B14" s="30" t="s">
         <v>617</v>
       </c>
     </row>

--- a/Excel+LAB+4+Dataset_Dmart_Cleaning_Structuring.xlsx
+++ b/Excel+LAB+4+Dataset_Dmart_Cleaning_Structuring.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8cfbbed923ba5ea5/Desktop/adv excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{84E5173C-E445-43B0-B4B8-93F9F631873B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E323197C-1E3D-4E0A-9BCC-E7551A744791}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{1DFF1FC6-F394-4EF5-8EAA-DC8CF110DDD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C4988E8-5187-40F2-8063-E4358151E54F}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,10 +18,14 @@
     <sheet name="Custom list" sheetId="4" r:id="rId3"/>
     <sheet name="Sheet5" sheetId="5" r:id="rId4"/>
     <sheet name="Sheet2" sheetId="6" r:id="rId5"/>
+    <sheet name="VLOOKUP" sheetId="7" r:id="rId6"/>
+    <sheet name="HLOOKUP" sheetId="8" r:id="rId7"/>
+    <sheet name="Data validation" sheetId="10" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="category">'DMart Data Sale'!$D:$D</definedName>
     <definedName name="discount">'DMart Data Sale'!$G:$G</definedName>
+    <definedName name="orderdate">Table1[[#Headers],[order_date]]</definedName>
     <definedName name="orderId">'DMart Data Sale'!$A:$A</definedName>
     <definedName name="region">'DMart Data Sale'!$B:$B</definedName>
     <definedName name="sales">'DMart Data Sale'!$E:$E</definedName>
@@ -42,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4603" uniqueCount="671">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4679" uniqueCount="712">
   <si>
     <t>Region</t>
   </si>
@@ -2055,6 +2059,129 @@
   </si>
   <si>
     <t>Total sales for customer type MEMBER and payment mode is UPI OR CARD</t>
+  </si>
+  <si>
+    <t>Total sales by North region</t>
+  </si>
+  <si>
+    <t>Total sales by South region</t>
+  </si>
+  <si>
+    <t>Total sales by East region</t>
+  </si>
+  <si>
+    <t>Total sales by West region</t>
+  </si>
+  <si>
+    <t>Number of orders North</t>
+  </si>
+  <si>
+    <t>Number of orders South</t>
+  </si>
+  <si>
+    <t>Number of orders East</t>
+  </si>
+  <si>
+    <t>Number of orders West</t>
+  </si>
+  <si>
+    <t>Total sales for yearv 2023</t>
+  </si>
+  <si>
+    <t>Last 6 months sales</t>
+  </si>
+  <si>
+    <t>Employee ID</t>
+  </si>
+  <si>
+    <t>Data</t>
+  </si>
+  <si>
+    <t>without hidden values</t>
+  </si>
+  <si>
+    <t>with hidden values</t>
+  </si>
+  <si>
+    <t>Total Sales</t>
+  </si>
+  <si>
+    <t>select filters</t>
+  </si>
+  <si>
+    <t>count</t>
+  </si>
+  <si>
+    <t>countblank</t>
+  </si>
+  <si>
+    <t>countA</t>
+  </si>
+  <si>
+    <t>Emp ID</t>
+  </si>
+  <si>
+    <t>Jan</t>
+  </si>
+  <si>
+    <t>Feb</t>
+  </si>
+  <si>
+    <t>Mar</t>
+  </si>
+  <si>
+    <t>Apr</t>
+  </si>
+  <si>
+    <t>Cost</t>
+  </si>
+  <si>
+    <t>Travel</t>
+  </si>
+  <si>
+    <t>Profit</t>
+  </si>
+  <si>
+    <t>Month</t>
+  </si>
+  <si>
+    <t>Using VLOOKUP</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Age </t>
+  </si>
+  <si>
+    <t>min</t>
+  </si>
+  <si>
+    <t>max</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Marks</t>
+  </si>
+  <si>
+    <t>OTP</t>
+  </si>
+  <si>
+    <t>JSD8</t>
+  </si>
+  <si>
+    <t>352W</t>
+  </si>
+  <si>
+    <t>GTR3</t>
+  </si>
+  <si>
+    <t>4WRW</t>
+  </si>
+  <si>
+    <t>Order ID</t>
   </si>
 </sst>
 </file>
@@ -2066,11 +2193,32 @@
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="&quot;₹&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2181,8 +2329,14 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2213,8 +2367,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="11">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -2332,86 +2504,128 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFA4A4A4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="15" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="18" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="16" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="19" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="28">
+  <dxfs count="33">
     <dxf>
       <fill>
         <patternFill>
@@ -2485,6 +2699,95 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color rgb="FF212529"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF4F4F4"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="medium">
+          <color rgb="FFA4A4A4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color rgb="FF212529"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF4F4F4"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FFA4A4A4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12.3"/>
+        <color rgb="FF333333"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFD8D8D8"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -3016,32 +3319,42 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:Q499" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26" tableBorderDxfId="25">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:Q499" totalsRowShown="0" headerRowDxfId="32" dataDxfId="31" tableBorderDxfId="30">
   <autoFilter ref="A1:Q499" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="f" dataDxfId="24"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Region" dataDxfId="23"/>
-    <tableColumn id="15" xr3:uid="{ACC19518-40CB-4AE8-B87C-D3C04DE1844C}" name="Updated region" dataDxfId="22"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Category" dataDxfId="21"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="sales" dataDxfId="20"/>
-    <tableColumn id="17" xr3:uid="{CCBA33DB-135B-4318-ABF2-BE5FFA4C3314}" name="sales category" dataDxfId="19">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="f" dataDxfId="29"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Region" dataDxfId="28"/>
+    <tableColumn id="15" xr3:uid="{ACC19518-40CB-4AE8-B87C-D3C04DE1844C}" name="Updated region" dataDxfId="27"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Category" dataDxfId="26"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="sales" dataDxfId="25"/>
+    <tableColumn id="17" xr3:uid="{CCBA33DB-135B-4318-ABF2-BE5FFA4C3314}" name="sales category" dataDxfId="24">
       <calculatedColumnFormula>IF(Table1[[#This Row],[sales]]&gt;=3000,"High sales",IF(Table1[[#This Row],[sales]]&gt;=1000,"Medium sales","Low"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="discount" dataDxfId="18"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="quantity" dataDxfId="17"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="order_date" dataDxfId="16"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="delivery_date" dataDxfId="15"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="customer_type" dataDxfId="14"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="customer_type2" dataDxfId="13"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="payment_mode" dataDxfId="12"/>
-    <tableColumn id="21" xr3:uid="{811674D1-ADD7-4EFB-AA4D-D76F047FBF99}" name="discount category" dataDxfId="11">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="discount" dataDxfId="23"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="quantity" dataDxfId="22"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="order_date" dataDxfId="21"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="delivery_date" dataDxfId="20"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="customer_type" dataDxfId="19"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="customer_type2" dataDxfId="18"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="payment_mode" dataDxfId="17"/>
+    <tableColumn id="21" xr3:uid="{811674D1-ADD7-4EFB-AA4D-D76F047FBF99}" name="discount category" dataDxfId="16">
       <calculatedColumnFormula>IF(AND(Table1[[#This Row],[customer_type]]="Member",OR(Table1[[#This Row],[payment_mode]]="UPI",Table1[[#This Row],[payment_mode]]="CARD")),"YES","NO")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="profit" dataDxfId="10"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Updated city" dataDxfId="9"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="city" dataDxfId="8"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="profit" dataDxfId="15"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Updated city" dataDxfId="14"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="city" dataDxfId="13"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{0D01C01F-0810-4586-ADAC-5676C7CAE3DA}" name="Table3" displayName="Table3" ref="A1:A7" totalsRowShown="0" headerRowDxfId="12" dataDxfId="10" headerRowBorderDxfId="11" tableBorderDxfId="9">
+  <autoFilter ref="A1:A7" xr:uid="{0D01C01F-0810-4586-ADAC-5676C7CAE3DA}"/>
+  <tableColumns count="1">
+    <tableColumn id="1" xr3:uid="{9B7D95F4-290C-4D81-8894-BA807B258DED}" name="Data" dataDxfId="8"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -3264,7 +3577,9 @@
     <col min="18" max="18" width="8.6328125" customWidth="1"/>
     <col min="19" max="19" width="67.36328125" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="20.90625" customWidth="1"/>
-    <col min="21" max="25" width="8.6328125" customWidth="1"/>
+    <col min="21" max="21" width="8.6328125" customWidth="1"/>
+    <col min="22" max="22" width="9.7265625" customWidth="1"/>
+    <col min="23" max="25" width="8.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -3393,7 +3708,7 @@
         <v>386412.25</v>
       </c>
       <c r="U2" s="1"/>
-      <c r="V2" s="1"/>
+      <c r="V2" s="51"/>
       <c r="W2" s="1"/>
       <c r="X2" s="1"/>
       <c r="Y2" s="1"/>
@@ -3463,7 +3778,7 @@
         <v>522964.3</v>
       </c>
       <c r="U3" s="1"/>
-      <c r="V3" s="1"/>
+      <c r="V3" s="51"/>
       <c r="W3" s="1"/>
       <c r="X3" s="1"/>
       <c r="Y3" s="1"/>
@@ -3660,15 +3975,15 @@
         <v>16</v>
       </c>
       <c r="R6" s="1"/>
-      <c r="S6" s="47" t="s">
+      <c r="S6" s="45" t="s">
         <v>659</v>
       </c>
       <c r="T6" s="44">
         <f>SUMIFS(sales,category,"Clothing",region,"East")</f>
         <v>60655.859999999993</v>
       </c>
-      <c r="U6" s="46"/>
-      <c r="V6" s="46"/>
+      <c r="U6" s="1"/>
+      <c r="V6" s="1"/>
       <c r="W6" s="1"/>
       <c r="X6" s="1"/>
       <c r="Y6" s="1"/>
@@ -3730,14 +4045,14 @@
         <v>34</v>
       </c>
       <c r="R7" s="1"/>
-      <c r="S7" s="47" t="s">
+      <c r="S7" s="45" t="s">
         <v>660</v>
       </c>
       <c r="T7" s="44">
         <f>SUMIFS(sales,category,"Electronics",region,"North",discount,"&gt;0.40")</f>
         <v>36091.269999999997</v>
       </c>
-      <c r="U7" s="46"/>
+      <c r="U7" s="1"/>
       <c r="W7" s="1"/>
       <c r="X7" s="1"/>
       <c r="Y7" s="1"/>
@@ -3864,7 +4179,7 @@
         <v>38</v>
       </c>
       <c r="R9" s="1"/>
-      <c r="S9" s="45" t="s">
+      <c r="S9" s="44" t="s">
         <v>661</v>
       </c>
       <c r="T9" s="44">
@@ -3934,7 +4249,7 @@
         <v>40</v>
       </c>
       <c r="R10" s="1"/>
-      <c r="S10" s="45" t="s">
+      <c r="S10" s="44" t="s">
         <v>662</v>
       </c>
       <c r="T10" s="44">
@@ -4004,7 +4319,7 @@
         <v>21</v>
       </c>
       <c r="R11" s="1"/>
-      <c r="S11" s="45" t="s">
+      <c r="S11" s="44" t="s">
         <v>663</v>
       </c>
       <c r="T11" s="44">
@@ -4074,7 +4389,7 @@
         <v>43</v>
       </c>
       <c r="R12" s="1"/>
-      <c r="S12" s="45" t="s">
+      <c r="S12" s="44" t="s">
         <v>664</v>
       </c>
       <c r="T12" s="44">
@@ -4209,7 +4524,7 @@
         <v>29</v>
       </c>
       <c r="R14" s="1"/>
-      <c r="S14" s="45" t="s">
+      <c r="S14" s="44" t="s">
         <v>665</v>
       </c>
       <c r="T14" s="44">
@@ -4278,7 +4593,7 @@
         <v>47</v>
       </c>
       <c r="R15" s="1"/>
-      <c r="S15" s="45" t="s">
+      <c r="S15" s="44" t="s">
         <v>666</v>
       </c>
       <c r="T15" s="44">
@@ -4347,7 +4662,7 @@
         <v>38</v>
       </c>
       <c r="R16" s="1"/>
-      <c r="S16" s="45" t="s">
+      <c r="S16" s="44" t="s">
         <v>667</v>
       </c>
       <c r="T16" s="44">
@@ -4416,7 +4731,7 @@
         <v>40</v>
       </c>
       <c r="R17" s="1"/>
-      <c r="S17" s="45" t="s">
+      <c r="S17" s="44" t="s">
         <v>668</v>
       </c>
       <c r="T17" s="44">
@@ -4485,7 +4800,7 @@
         <v>51</v>
       </c>
       <c r="R18" s="1"/>
-      <c r="S18" s="45" t="s">
+      <c r="S18" s="44" t="s">
         <v>669</v>
       </c>
       <c r="T18" s="44">
@@ -4619,7 +4934,7 @@
         <v>54</v>
       </c>
       <c r="R20" s="1"/>
-      <c r="S20" s="45" t="s">
+      <c r="S20" s="44" t="s">
         <v>670</v>
       </c>
       <c r="T20" s="26" t="s">
@@ -4764,7 +5079,10 @@
         <v>57</v>
       </c>
       <c r="R22" s="1"/>
-      <c r="T22" s="1"/>
+      <c r="T22" s="44">
+        <f>SUMIF(region,"North",sales)</f>
+        <v>334964.16000000003</v>
+      </c>
       <c r="U22" s="1"/>
       <c r="V22" s="1"/>
       <c r="W22" s="1"/>
@@ -4828,8 +5146,9 @@
         <v>38</v>
       </c>
       <c r="R23" s="1"/>
-      <c r="S23" s="1"/>
-      <c r="T23" s="1"/>
+      <c r="S23" s="44" t="s">
+        <v>671</v>
+      </c>
       <c r="U23" s="1"/>
       <c r="V23" s="1"/>
       <c r="W23" s="1"/>
@@ -4893,8 +5212,13 @@
         <v>40</v>
       </c>
       <c r="R24" s="1"/>
-      <c r="S24" s="1"/>
-      <c r="T24" s="1"/>
+      <c r="S24" s="44" t="s">
+        <v>672</v>
+      </c>
+      <c r="T24" s="44">
+        <f>SUMIF(region,"South",sales)</f>
+        <v>303623.68999999994</v>
+      </c>
       <c r="U24" s="1"/>
       <c r="V24" s="1"/>
       <c r="W24" s="1"/>
@@ -4958,8 +5282,13 @@
         <v>34</v>
       </c>
       <c r="R25" s="1"/>
-      <c r="S25" s="1"/>
-      <c r="T25" s="1"/>
+      <c r="S25" s="44" t="s">
+        <v>673</v>
+      </c>
+      <c r="T25" s="44">
+        <f>SUMIF(region,"East",sales)</f>
+        <v>337881.26999999996</v>
+      </c>
       <c r="U25" s="1"/>
       <c r="V25" s="1"/>
       <c r="W25" s="1"/>
@@ -5023,8 +5352,13 @@
         <v>62</v>
       </c>
       <c r="R26" s="1"/>
-      <c r="S26" s="1"/>
-      <c r="T26" s="1"/>
+      <c r="S26" s="44" t="s">
+        <v>674</v>
+      </c>
+      <c r="T26" s="44">
+        <f>SUMIF(region,"West",sales)</f>
+        <v>346200.06999999983</v>
+      </c>
       <c r="U26" s="1"/>
       <c r="V26" s="1"/>
       <c r="W26" s="1"/>
@@ -5153,8 +5487,13 @@
         <v>57</v>
       </c>
       <c r="R28" s="1"/>
-      <c r="S28" s="1"/>
-      <c r="T28" s="1"/>
+      <c r="S28" s="44" t="s">
+        <v>675</v>
+      </c>
+      <c r="T28" s="44">
+        <f>COUNTIF(region,"North")</f>
+        <v>124</v>
+      </c>
       <c r="U28" s="1"/>
       <c r="V28" s="1"/>
       <c r="W28" s="1"/>
@@ -5218,8 +5557,13 @@
         <v>67</v>
       </c>
       <c r="R29" s="1"/>
-      <c r="S29" s="1"/>
-      <c r="T29" s="1"/>
+      <c r="S29" s="44" t="s">
+        <v>676</v>
+      </c>
+      <c r="T29" s="44">
+        <f>COUNTIF(region,"South")</f>
+        <v>124</v>
+      </c>
       <c r="U29" s="1"/>
       <c r="V29" s="1"/>
       <c r="W29" s="1"/>
@@ -5283,8 +5627,13 @@
         <v>40</v>
       </c>
       <c r="R30" s="1"/>
-      <c r="S30" s="1"/>
-      <c r="T30" s="1"/>
+      <c r="S30" s="44" t="s">
+        <v>677</v>
+      </c>
+      <c r="T30" s="44">
+        <f>COUNTIF(region,"East")</f>
+        <v>125</v>
+      </c>
       <c r="U30" s="1"/>
       <c r="V30" s="1"/>
       <c r="W30" s="1"/>
@@ -5348,8 +5697,13 @@
         <v>34</v>
       </c>
       <c r="R31" s="1"/>
-      <c r="S31" s="1"/>
-      <c r="T31" s="1"/>
+      <c r="S31" s="44" t="s">
+        <v>678</v>
+      </c>
+      <c r="T31" s="44">
+        <f>COUNTIF(region,"West")</f>
+        <v>125</v>
+      </c>
       <c r="U31" s="1"/>
       <c r="V31" s="1"/>
       <c r="W31" s="1"/>
@@ -5478,8 +5832,13 @@
         <v>16</v>
       </c>
       <c r="R33" s="1"/>
-      <c r="S33" s="1"/>
-      <c r="T33" s="1"/>
+      <c r="S33" s="44" t="s">
+        <v>679</v>
+      </c>
+      <c r="T33" s="26">
+        <f>SUMIF(I:I,"&lt;2024-01-01",sales)</f>
+        <v>654586.69000000018</v>
+      </c>
       <c r="U33" s="1"/>
       <c r="V33" s="1"/>
       <c r="W33" s="1"/>
@@ -5543,8 +5902,13 @@
         <v>54</v>
       </c>
       <c r="R34" s="1"/>
-      <c r="S34" s="1"/>
-      <c r="T34" s="1"/>
+      <c r="S34" s="44" t="s">
+        <v>680</v>
+      </c>
+      <c r="T34" s="26">
+        <f>SUMIF(I:I,"&gt;=2024-07-01",sales)</f>
+        <v>368049.34999999992</v>
+      </c>
       <c r="U34" s="1"/>
       <c r="V34" s="1"/>
       <c r="W34" s="1"/>
@@ -5608,8 +5972,13 @@
         <v>26</v>
       </c>
       <c r="R35" s="1"/>
-      <c r="S35" s="1"/>
-      <c r="T35" s="1"/>
+      <c r="S35" s="44" t="s">
+        <v>680</v>
+      </c>
+      <c r="T35" s="44">
+        <f>SUMIFS(Table1[sales],Table1[order_date],"&gt;=2024-07-01",Table1[order_date],"&lt;=2024-12-31")</f>
+        <v>368049.34999999992</v>
+      </c>
       <c r="U35" s="1"/>
       <c r="V35" s="1"/>
       <c r="W35" s="1"/>
@@ -5674,7 +6043,6 @@
       </c>
       <c r="R36" s="1"/>
       <c r="S36" s="1"/>
-      <c r="T36" s="1"/>
       <c r="U36" s="1"/>
       <c r="V36" s="1"/>
       <c r="W36" s="1"/>
@@ -5739,7 +6107,10 @@
       </c>
       <c r="R37" s="1"/>
       <c r="S37" s="1"/>
-      <c r="T37" s="1"/>
+      <c r="T37" s="46">
+        <f>MAX(I:I)</f>
+        <v>45657</v>
+      </c>
       <c r="U37" s="1"/>
       <c r="V37" s="1"/>
       <c r="W37" s="1"/>
@@ -5868,8 +6239,12 @@
         <v>78</v>
       </c>
       <c r="R39" s="1"/>
-      <c r="S39" s="1"/>
-      <c r="T39" s="1"/>
+      <c r="S39" s="59" t="s">
+        <v>711</v>
+      </c>
+      <c r="T39" s="60" t="s">
+        <v>588</v>
+      </c>
       <c r="U39" s="1"/>
       <c r="V39" s="1"/>
       <c r="W39" s="1"/>
@@ -5933,8 +6308,13 @@
         <v>34</v>
       </c>
       <c r="R40" s="1"/>
-      <c r="S40" s="1"/>
-      <c r="T40" s="1"/>
+      <c r="S40" s="61" t="s">
+        <v>11</v>
+      </c>
+      <c r="T40" s="51">
+        <f>VLOOKUP(S40,Table1[#All],MATCH(T39,Table1[#Headers],0),FALSE)</f>
+        <v>713.49</v>
+      </c>
       <c r="U40" s="1"/>
       <c r="V40" s="1"/>
       <c r="W40" s="1"/>
@@ -35644,8 +36024,13 @@
       <c r="Y500" s="1"/>
     </row>
     <row r="501" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A501" s="1"/>
-      <c r="B501" s="2"/>
+      <c r="A501" s="51" t="s">
+        <v>685</v>
+      </c>
+      <c r="B501" s="2">
+        <f>SUM(sales)</f>
+        <v>1322669.1900000023</v>
+      </c>
       <c r="C501" s="2"/>
       <c r="D501" s="1"/>
       <c r="E501" s="1"/>
@@ -35671,8 +36056,13 @@
       <c r="Y501" s="1"/>
     </row>
     <row r="502" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A502" s="1"/>
-      <c r="B502" s="2"/>
+      <c r="A502" s="51" t="s">
+        <v>683</v>
+      </c>
+      <c r="B502" s="2">
+        <f>SUBTOTAL(9,sales)</f>
+        <v>1322669.1900000023</v>
+      </c>
       <c r="C502" s="2"/>
       <c r="D502" s="1"/>
       <c r="E502" s="1"/>
@@ -35699,7 +36089,9 @@
     </row>
     <row r="503" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A503" s="1"/>
-      <c r="B503" s="2"/>
+      <c r="B503" s="52" t="s">
+        <v>686</v>
+      </c>
       <c r="C503" s="2"/>
       <c r="D503" s="1"/>
       <c r="E503" s="1"/>
@@ -49144,7 +49536,7 @@
       <c r="Y1000" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="11" type="noConversion"/>
   <conditionalFormatting sqref="E1:F490 F3:F499">
     <cfRule type="top10" dxfId="7" priority="4" bottom="1" rank="10"/>
   </conditionalFormatting>
@@ -49743,7 +50135,10 @@
         <f>IF(L15&gt;=75000,"15%",IF(L15&gt;=70000,"10%",IF(L15&gt;=50000,"5%",IF(L15&lt;50000,"no bonus"))))</f>
         <v>10%</v>
       </c>
-      <c r="N15" s="26"/>
+      <c r="N15" s="26">
+        <f>L15*M15</f>
+        <v>7000</v>
+      </c>
       <c r="P15" s="33"/>
       <c r="Q15">
         <v>75000</v>
@@ -49779,7 +50174,10 @@
         <f>IF(L16&gt;=75000,"15%",IF(L16&gt;=70000,"10%",IF(L16&gt;=50000,"5%",IF(L16&lt;50000,"no bonus"))))</f>
         <v>5%</v>
       </c>
-      <c r="N16" s="26"/>
+      <c r="N16" s="26">
+        <f>L16*M16</f>
+        <v>2500</v>
+      </c>
       <c r="P16" s="33"/>
       <c r="Q16">
         <v>70000</v>
@@ -49812,10 +50210,13 @@
         <v>45000</v>
       </c>
       <c r="M17" s="26" t="str">
-        <f>IF(L17&gt;=75000,"15%",IF(L17&gt;=70000,"10%",IF(L17&gt;=50000,"5%",IF(L17&lt;50000,"no bonus"))))</f>
-        <v>no bonus</v>
-      </c>
-      <c r="N17" s="26"/>
+        <f>IF(L17&gt;=75000,"15%",IF(L17&gt;=70000,"10%",IF(L17&gt;=50000,"5%",IF(L17&lt;50000,"0%"))))</f>
+        <v>0%</v>
+      </c>
+      <c r="N17" s="26">
+        <f>L17*M17</f>
+        <v>0</v>
+      </c>
       <c r="O17" s="31"/>
       <c r="P17" s="33"/>
       <c r="Q17">
@@ -49858,7 +50259,10 @@
         <f>IF(L18&gt;=75000,"15%",IF(L18&gt;=70000,"10%",IF(L18&gt;=50000,"5%",IF(L18&lt;50000,"no bonus"))))</f>
         <v>15%</v>
       </c>
-      <c r="N18" s="26"/>
+      <c r="N18" s="26">
+        <f>L18*M18</f>
+        <v>11250</v>
+      </c>
       <c r="Q18" s="31" t="s">
         <v>639</v>
       </c>
@@ -49893,7 +50297,10 @@
         <f>IF(L19&gt;=75000,"15%",IF(L19&gt;=70000,"10%",IF(L19&gt;=50000,"5%",IF(L19&lt;50000,"no bonus"))))</f>
         <v>5%</v>
       </c>
-      <c r="N19" s="26"/>
+      <c r="N19" s="26">
+        <f>L19*M19</f>
+        <v>2750</v>
+      </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A20" s="26" t="s">
@@ -49918,6 +50325,17 @@
       <c r="B22" s="26">
         <v>47927</v>
       </c>
+      <c r="D22" s="26" t="s">
+        <v>615</v>
+      </c>
+      <c r="E22" s="26" t="s">
+        <v>592</v>
+      </c>
+      <c r="F22" s="26" t="s">
+        <v>681</v>
+      </c>
+      <c r="G22" s="26"/>
+      <c r="H22" s="26"/>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A23" s="26" t="s">
@@ -49926,6 +50344,20 @@
       <c r="B23" s="26">
         <v>94899</v>
       </c>
+      <c r="D23" s="26" t="s">
+        <v>591</v>
+      </c>
+      <c r="E23" s="26" t="s">
+        <v>593</v>
+      </c>
+      <c r="F23" s="26">
+        <v>1001</v>
+      </c>
+      <c r="G23" s="26"/>
+      <c r="H23" s="26">
+        <f>COUNTIF(F23:F26,F23)</f>
+        <v>2</v>
+      </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A24" s="26" t="s">
@@ -49934,6 +50366,17 @@
       <c r="B24" s="26">
         <v>84290</v>
       </c>
+      <c r="D24" s="26" t="s">
+        <v>588</v>
+      </c>
+      <c r="E24" s="26" t="s">
+        <v>595</v>
+      </c>
+      <c r="F24" s="26">
+        <v>1002</v>
+      </c>
+      <c r="G24" s="26"/>
+      <c r="H24" s="26"/>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A25" s="26" t="s">
@@ -49942,6 +50385,17 @@
       <c r="B25" s="26">
         <v>80950</v>
       </c>
+      <c r="D25" s="26" t="s">
+        <v>590</v>
+      </c>
+      <c r="E25" s="26" t="s">
+        <v>594</v>
+      </c>
+      <c r="F25" s="26">
+        <v>1001</v>
+      </c>
+      <c r="G25" s="26"/>
+      <c r="H25" s="26"/>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A26" s="26" t="s">
@@ -49950,12 +50404,23 @@
       <c r="B26" s="26">
         <v>59860</v>
       </c>
+      <c r="D26" s="26" t="s">
+        <v>589</v>
+      </c>
+      <c r="E26" s="26" t="s">
+        <v>595</v>
+      </c>
+      <c r="F26" s="26">
+        <v>1002</v>
+      </c>
+      <c r="G26" s="26"/>
+      <c r="H26" s="26"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A19:B26">
     <sortCondition ref="A19:A26" customList="January,February,March,April,May,June,July,August,September,October,November,December"/>
   </sortState>
-  <phoneticPr fontId="12" type="noConversion"/>
+  <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -50119,6 +50584,8 @@
       <c r="B10" s="30" t="s">
         <v>594</v>
       </c>
+      <c r="D10" s="47"/>
+      <c r="E10" s="47"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" s="30" t="s">
@@ -50127,6 +50594,7 @@
       <c r="B11" s="30" t="s">
         <v>618</v>
       </c>
+      <c r="D11" s="47"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" s="26" t="s">
@@ -50135,6 +50603,7 @@
       <c r="B12" s="30" t="s">
         <v>598</v>
       </c>
+      <c r="D12" s="47"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" s="26" t="s">
@@ -50153,16 +50622,617 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="12" type="noConversion"/>
+  <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CF2FC65-AC86-4D81-AD93-6FE36BA264EB}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="11.453125" customWidth="1"/>
+    <col min="2" max="2" width="18.453125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="20" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="49" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="47">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="47">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="47">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="47">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="47">
+        <v>45</v>
+      </c>
+      <c r="B6" s="48"/>
+      <c r="C6" s="48"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="47">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B9" s="50" t="s">
+        <v>684</v>
+      </c>
+      <c r="C9">
+        <f>SUBTOTAL(9,A2:A7)</f>
+        <v>578</v>
+      </c>
+      <c r="D9">
+        <f>SUBTOTAL(1,Table3[Data])</f>
+        <v>96.333333333333329</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B10" s="50" t="s">
+        <v>683</v>
+      </c>
+      <c r="C10">
+        <f>SUBTOTAL(109,Table3[Data])</f>
+        <v>578</v>
+      </c>
+      <c r="D10">
+        <f>SUBTOTAL(101,Table3[Data])</f>
+        <v>96.333333333333329</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" s="29" t="s">
+        <v>687</v>
+      </c>
+      <c r="B22" s="26">
+        <f>COUNT(A12:A20)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" s="29" t="s">
+        <v>688</v>
+      </c>
+      <c r="B23" s="26">
+        <f>COUNTBLANK(A12:A20)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" s="29" t="s">
+        <v>689</v>
+      </c>
+      <c r="B24" s="26">
+        <f>COUNTA(A12:A20)</f>
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C1366A4-CD61-49CD-BBAA-9D7083F6C4AD}">
+  <dimension ref="A2:E10"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="4" max="4" width="12.6328125" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" s="26" t="s">
+        <v>690</v>
+      </c>
+      <c r="B2" s="32" t="s">
+        <v>619</v>
+      </c>
+      <c r="C2" s="32" t="s">
+        <v>637</v>
+      </c>
+      <c r="D2" s="32" t="s">
+        <v>638</v>
+      </c>
+      <c r="E2" s="32" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" s="26">
+        <v>1001</v>
+      </c>
+      <c r="B3" s="32" t="s">
+        <v>622</v>
+      </c>
+      <c r="C3" s="26">
+        <v>70000</v>
+      </c>
+      <c r="D3" s="26" t="str">
+        <f>IF(C3&gt;=75000,"15%",IF(C3&gt;=70000,"10%",IF(C3&gt;=50000,"5%",IF(C3&lt;50000,"no bonus"))))</f>
+        <v>10%</v>
+      </c>
+      <c r="E3" s="26">
+        <f>C3*D3</f>
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" s="26">
+        <v>1002</v>
+      </c>
+      <c r="B4" s="32" t="s">
+        <v>623</v>
+      </c>
+      <c r="C4" s="26">
+        <v>50000</v>
+      </c>
+      <c r="D4" s="26" t="str">
+        <f>IF(C4&gt;=75000,"15%",IF(C4&gt;=70000,"10%",IF(C4&gt;=50000,"5%",IF(C4&lt;50000,"no bonus"))))</f>
+        <v>5%</v>
+      </c>
+      <c r="E4" s="26">
+        <f>C4*D4</f>
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" s="26">
+        <v>1003</v>
+      </c>
+      <c r="B5" s="32" t="s">
+        <v>624</v>
+      </c>
+      <c r="C5" s="26">
+        <v>45000</v>
+      </c>
+      <c r="D5" s="26" t="str">
+        <f>IF(C5&gt;=75000,"15%",IF(C5&gt;=70000,"10%",IF(C5&gt;=50000,"5%",IF(C5&lt;50000,"0%"))))</f>
+        <v>0%</v>
+      </c>
+      <c r="E5" s="26">
+        <f>C5*D5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" s="26">
+        <v>1004</v>
+      </c>
+      <c r="B6" s="32" t="s">
+        <v>625</v>
+      </c>
+      <c r="C6" s="26">
+        <v>75000</v>
+      </c>
+      <c r="D6" s="26" t="str">
+        <f>IF(C6&gt;=75000,"15%",IF(C6&gt;=70000,"10%",IF(C6&gt;=50000,"5%",IF(C6&lt;50000,"no bonus"))))</f>
+        <v>15%</v>
+      </c>
+      <c r="E6" s="26">
+        <f>C6*D6</f>
+        <v>11250</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" s="26">
+        <v>1005</v>
+      </c>
+      <c r="B7" s="32" t="s">
+        <v>626</v>
+      </c>
+      <c r="C7" s="26">
+        <v>55000</v>
+      </c>
+      <c r="D7" s="26" t="str">
+        <f>IF(C7&gt;=75000,"15%",IF(C7&gt;=70000,"10%",IF(C7&gt;=50000,"5%",IF(C7&lt;50000,"no bonus"))))</f>
+        <v>5%</v>
+      </c>
+      <c r="E7" s="26">
+        <f>C7*D7</f>
+        <v>2750</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B9" s="53" t="s">
+        <v>690</v>
+      </c>
+      <c r="C9" s="53" t="s">
+        <v>588</v>
+      </c>
+      <c r="D9" s="53" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B10" s="26">
+        <v>1004</v>
+      </c>
+      <c r="C10" s="26">
+        <f>VLOOKUP(B10,A2:E7,3,FALSE)</f>
+        <v>75000</v>
+      </c>
+      <c r="D10" s="26">
+        <f>VLOOKUP(B10,A3:E7,5,FALSE)</f>
+        <v>11250</v>
+      </c>
+      <c r="E10">
+        <f>MATCH(B6,B2:B7,0)</f>
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B10" xr:uid="{72BFE547-1A68-43CF-B92F-D35D6D775F4A}">
+      <formula1>$A$3:$A$7</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58A7EA64-1B71-4820-8E66-B7EBC569D24E}">
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" s="26"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" s="26"/>
+      <c r="B2" s="29" t="s">
+        <v>691</v>
+      </c>
+      <c r="C2" s="29" t="s">
+        <v>692</v>
+      </c>
+      <c r="D2" s="29" t="s">
+        <v>693</v>
+      </c>
+      <c r="E2" s="29" t="s">
+        <v>694</v>
+      </c>
+      <c r="F2" s="29" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="29" t="s">
+        <v>695</v>
+      </c>
+      <c r="B3" s="26">
+        <v>100</v>
+      </c>
+      <c r="C3" s="26">
+        <v>585</v>
+      </c>
+      <c r="D3" s="26">
+        <v>333</v>
+      </c>
+      <c r="E3" s="26">
+        <v>745</v>
+      </c>
+      <c r="F3" s="26">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" s="29" t="s">
+        <v>696</v>
+      </c>
+      <c r="B4" s="26">
+        <v>100</v>
+      </c>
+      <c r="C4" s="26">
+        <v>500</v>
+      </c>
+      <c r="D4" s="26">
+        <v>600</v>
+      </c>
+      <c r="E4" s="26">
+        <v>700</v>
+      </c>
+      <c r="F4" s="26">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="29" t="s">
+        <v>588</v>
+      </c>
+      <c r="B5" s="26">
+        <v>2000</v>
+      </c>
+      <c r="C5" s="26">
+        <v>7000</v>
+      </c>
+      <c r="D5" s="26">
+        <v>8000</v>
+      </c>
+      <c r="E5" s="26">
+        <v>6000</v>
+      </c>
+      <c r="F5" s="26">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="29" t="s">
+        <v>697</v>
+      </c>
+      <c r="B6" s="26">
+        <v>400</v>
+      </c>
+      <c r="C6" s="26">
+        <v>500</v>
+      </c>
+      <c r="D6" s="26">
+        <v>300</v>
+      </c>
+      <c r="E6" s="26">
+        <v>300</v>
+      </c>
+      <c r="F6" s="26">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F8" s="54" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B9" s="27" t="s">
+        <v>698</v>
+      </c>
+      <c r="C9" s="54" t="s">
+        <v>691</v>
+      </c>
+      <c r="D9" s="54"/>
+      <c r="F9" s="54" t="s">
+        <v>698</v>
+      </c>
+      <c r="G9" s="54" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B10" s="27" t="s">
+        <v>588</v>
+      </c>
+      <c r="C10">
+        <f>HLOOKUP($C$9,$A$2:$F$6,MATCH(B10,$A$2:$A$6,0),FALSE)</f>
+        <v>2000</v>
+      </c>
+      <c r="F10" s="54" t="s">
+        <v>588</v>
+      </c>
+      <c r="G10">
+        <f>VLOOKUP(F10,A3:F6,MATCH(G9,A2:FC2,0),FALSE)</f>
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B11" s="27" t="s">
+        <v>696</v>
+      </c>
+      <c r="C11">
+        <f>HLOOKUP($C$9,$A$2:$F$6,MATCH(B11,$A$2:$A$6,0),FALSE)</f>
+        <v>100</v>
+      </c>
+      <c r="F11" s="54" t="s">
+        <v>697</v>
+      </c>
+      <c r="G11">
+        <f>VLOOKUP(F11,A2:F6,MATCH(G9,A2:FC2,0),FALSE)</f>
+        <v>200</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="11" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D90FA85-CDB8-408B-9988-10E5B4EC3DF5}">
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="3" max="3" width="10.08984375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" s="57" t="s">
+        <v>701</v>
+      </c>
+      <c r="B1" s="57" t="s">
+        <v>700</v>
+      </c>
+      <c r="C1" s="57" t="s">
+        <v>704</v>
+      </c>
+      <c r="D1" s="57" t="s">
+        <v>705</v>
+      </c>
+      <c r="E1" s="57" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" s="26">
+        <v>55</v>
+      </c>
+      <c r="B2" s="26">
+        <v>2</v>
+      </c>
+      <c r="C2" s="58">
+        <v>46214</v>
+      </c>
+      <c r="D2" s="26"/>
+      <c r="E2" s="55" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" s="26">
+        <v>44</v>
+      </c>
+      <c r="B3" s="26">
+        <v>4</v>
+      </c>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="55" t="s">
+        <v>708</v>
+      </c>
+      <c r="G3" s="56" t="s">
+        <v>702</v>
+      </c>
+      <c r="H3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" s="26">
+        <v>34</v>
+      </c>
+      <c r="B4" s="26">
+        <v>3</v>
+      </c>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26">
+        <v>3423</v>
+      </c>
+      <c r="G4" s="56" t="s">
+        <v>703</v>
+      </c>
+      <c r="H4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" s="26">
+        <v>43</v>
+      </c>
+      <c r="B5" s="26">
+        <v>4</v>
+      </c>
+      <c r="C5" s="26"/>
+      <c r="D5" s="26"/>
+      <c r="E5" s="55" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" s="26">
+        <v>56</v>
+      </c>
+      <c r="B6" s="26">
+        <v>5</v>
+      </c>
+      <c r="C6" s="26"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26">
+        <v>5232</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" s="26">
+        <v>13</v>
+      </c>
+      <c r="B7" s="26">
+        <v>6</v>
+      </c>
+      <c r="C7" s="26"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="55" t="s">
+        <v>710</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="6">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Quantity error" error="Invalid entry for quantity" promptTitle="Quantity" prompt="Enter Quantity between 2 and 10" sqref="B1:B1048576" xr:uid="{BC0545D4-1DD0-4319-9CFF-8ADFED21D76E}">
+      <formula1>2</formula1>
+      <formula2>10</formula2>
+    </dataValidation>
+    <dataValidation type="date" operator="lessThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Date" error="Invalid date" promptTitle="Date" prompt="Date should be less than today's date" sqref="C1:C1048576" xr:uid="{B7FECC5D-2584-4555-BB95-8D17D4BCB9A7}">
+      <formula1>46218</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Marks" error="INVALID marks" promptTitle="Marks" prompt="marks more than 45 and less than or equal to 75_x000a_" sqref="D1:D1048576" xr:uid="{5848DF8E-E369-400F-99D7-97AD6BD7DFEA}">
+      <formula1>AND(D2&gt;40,D2&lt;=75)</formula1>
+    </dataValidation>
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A8:A1048576" xr:uid="{FCC10A64-3E29-4E61-BAC0-8DB025C12247}">
+      <formula1>$H$3</formula1>
+      <formula2>$H$4</formula2>
+    </dataValidation>
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Age" error="Invalid Age" promptTitle="Age" prompt="Age is between 13 to 60" sqref="A1:A7" xr:uid="{C12E3780-BFDB-4D2F-ABD9-EB25CC6A9CF8}">
+      <formula1>$H$3</formula1>
+      <formula2>$H$4</formula2>
+    </dataValidation>
+    <dataValidation type="textLength" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="OTP" error="Invalid OTP" promptTitle="OTP" prompt="OTP should be of 4 digits" sqref="E1:E1048576" xr:uid="{E830B2A0-7258-4402-8BA7-A5E5CECD50E1}">
+      <formula1>4</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>